--- a/diseases/d043/2020-2025.xlsx
+++ b/diseases/d043/2020-2025.xlsx
@@ -6241,9 +6241,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6785,9 +6782,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7329,9 +7323,6 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -7873,9 +7864,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -8417,9 +8405,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8961,9 +8946,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -9505,9 +9487,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10049,9 +10028,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -10593,9 +10569,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11137,9 +11110,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -11829,9 +11799,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -12521,9 +12488,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -13213,9 +13177,6 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01793188037283966</v>
       </c>
@@ -13905,9 +13866,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14597,9 +14555,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15289,9 +15244,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.01793188037283966</v>
       </c>
@@ -15981,9 +15933,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16673,9 +16622,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17365,9 +17311,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18057,9 +18000,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -18749,9 +18689,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -19441,9 +19378,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20133,9 +20067,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -20825,9 +20756,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -21517,9 +21445,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -22209,9 +22134,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -22901,9 +22823,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -23593,9 +23512,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -24285,9 +24201,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -24977,9 +24890,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -25669,9 +25579,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -26361,9 +26268,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -27053,9 +26957,6 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.01778387646181242</v>
       </c>
@@ -27745,9 +27646,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -28437,9 +28335,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -29127,9 +29022,6 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
